--- a/exercices/exercice_gini_fortune_afc2022.xlsx
+++ b/exercices/exercice_gini_fortune_afc2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641C124B-9440-4BD0-B866-49B453A09288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E636784-BC16-4221-984D-34BA21BE7D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,6 @@
     <definedName name="_Ref522109637" localSheetId="0">Einleitung!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1132,10 +1131,10 @@
     <t>y_bar_above_T</t>
   </si>
   <si>
-    <t>total income 1%</t>
+    <t>interpolation lineaire</t>
   </si>
   <si>
-    <t>interpolation lineaire</t>
+    <t>Revenu total 1%</t>
   </si>
 </sst>
 </file>
@@ -1823,12 +1822,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
@@ -1848,6 +1841,12 @@
     </xf>
     <xf numFmtId="167" fontId="2" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2478,416 +2477,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'gini ch'!$L$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Proportion  des contribuables ayant un revenu supérieur au seuil inférieur du groupe</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'gini ch'!$L$6:$L$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.10972341132993091</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.3236309917479962</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.42331954997525389</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.55909433751016524</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-0.83867658047400384</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-1.1578223544713198</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-1.5371877741882165</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-1.762682114928541</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-2.0466180481520198</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-2.4294097756605804</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'gini ch'!$L$5:$L$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.10972341132993091</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.3236309917479962</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.42331954997525389</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-0.55909433751016524</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-0.83867658047400384</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-1.1578223544713198</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-1.5371877741882165</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-1.762682114928541</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-2.0466180481520198</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-2.4294097756605804</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E71D-4636-8AE6-22C3B924500D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="63930111"/>
-        <c:axId val="63932511"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="63930111"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="63932511"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="63932511"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="63930111"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3443,536 +3033,20 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>225335</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>286964</xdr:rowOff>
+      <xdr:colOff>170394</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>28133</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>479673</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>115897</xdr:rowOff>
+      <xdr:colOff>431082</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>33071</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3992,42 +3066,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>69023</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>349961</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>44598</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>115743</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Graphique 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C12BA0F5-D93B-36D7-4093-8E05F7BDDA30}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4324,16 +3362,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB30C28-FB64-45EE-8330-1613430D0A70}">
   <dimension ref="A1:D126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="20" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="74.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="9"/>
+    <col min="1" max="1" width="4.81640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="74.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="11.453125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>274</v>
       </c>
@@ -4341,13 +3379,13 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -4357,7 +3395,7 @@
       <c r="C3" s="11"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="8" t="s">
         <v>45</v>
@@ -4365,7 +3403,7 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
     </row>
-    <row r="5" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="8" t="s">
         <v>275</v>
@@ -4373,7 +3411,7 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="8" t="s">
         <v>46</v>
@@ -4381,7 +3419,7 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
         <v>47</v>
@@ -4389,7 +3427,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="8" t="s">
         <v>48</v>
@@ -4397,7 +3435,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="8" t="s">
         <v>49</v>
@@ -4405,13 +3443,13 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>2</v>
       </c>
@@ -4421,7 +3459,7 @@
       <c r="C11" s="11"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="8" t="s">
         <v>51</v>
@@ -4429,7 +3467,7 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="12" t="s">
         <v>52</v>
@@ -4437,7 +3475,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="8" t="s">
         <v>276</v>
@@ -4445,7 +3483,7 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
       <c r="B15" s="8" t="s">
         <v>53</v>
@@ -4453,7 +3491,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
       <c r="B16" s="8" t="s">
         <v>54</v>
@@ -4461,7 +3499,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
       <c r="B17" s="8" t="s">
         <v>55</v>
@@ -4469,7 +3507,7 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
       <c r="B18" s="8" t="s">
         <v>56</v>
@@ -4477,7 +3515,7 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
       <c r="B19" s="8" t="s">
         <v>57</v>
@@ -4485,7 +3523,7 @@
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
       <c r="B20" s="8" t="s">
         <v>58</v>
@@ -4493,7 +3531,7 @@
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
     </row>
-    <row r="21" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6"/>
       <c r="B21" s="8" t="s">
         <v>59</v>
@@ -4501,7 +3539,7 @@
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
       <c r="B22" s="8" t="s">
         <v>60</v>
@@ -4509,7 +3547,7 @@
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="8" t="s">
         <v>61</v>
@@ -4517,7 +3555,7 @@
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
       <c r="B24" s="8" t="s">
         <v>62</v>
@@ -4525,7 +3563,7 @@
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6"/>
       <c r="B25" s="8" t="s">
         <v>63</v>
@@ -4533,13 +3571,13 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>
       <c r="B27" s="13" t="s">
         <v>64</v>
@@ -4547,7 +3585,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6"/>
       <c r="B28" s="14" t="s">
         <v>65</v>
@@ -4555,7 +3593,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6"/>
       <c r="B29" s="8" t="s">
         <v>66</v>
@@ -4563,7 +3601,7 @@
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6"/>
       <c r="B30" s="8" t="s">
         <v>67</v>
@@ -4571,7 +3609,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
       <c r="B31" s="8" t="s">
         <v>68</v>
@@ -4579,7 +3617,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
       <c r="B32" s="8" t="s">
         <v>69</v>
@@ -4587,13 +3625,13 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6"/>
       <c r="B34" s="13" t="s">
         <v>70</v>
@@ -4601,7 +3639,7 @@
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
     </row>
-    <row r="35" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6"/>
       <c r="B35" s="14" t="s">
         <v>71</v>
@@ -4609,7 +3647,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6"/>
       <c r="B36" s="8" t="s">
         <v>72</v>
@@ -4617,7 +3655,7 @@
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6"/>
       <c r="B37" s="8" t="s">
         <v>73</v>
@@ -4625,13 +3663,13 @@
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6"/>
       <c r="B39" s="13" t="s">
         <v>74</v>
@@ -4639,7 +3677,7 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6"/>
       <c r="B40" s="14" t="s">
         <v>75</v>
@@ -4647,7 +3685,7 @@
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
     </row>
-    <row r="41" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6"/>
       <c r="B41" s="14" t="s">
         <v>76</v>
@@ -4655,7 +3693,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6"/>
       <c r="B42" s="8" t="s">
         <v>77</v>
@@ -4663,7 +3701,7 @@
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
     </row>
-    <row r="43" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
       <c r="B43" s="8" t="s">
         <v>78</v>
@@ -4671,7 +3709,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6"/>
       <c r="B44" s="8" t="s">
         <v>79</v>
@@ -4679,7 +3717,7 @@
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
     </row>
-    <row r="45" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6"/>
       <c r="B45" s="8" t="s">
         <v>80</v>
@@ -4687,7 +3725,7 @@
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6"/>
       <c r="B46" s="8" t="s">
         <v>81</v>
@@ -4695,7 +3733,7 @@
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
     </row>
-    <row r="47" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6"/>
       <c r="B47" s="8" t="s">
         <v>82</v>
@@ -4703,7 +3741,7 @@
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
     </row>
-    <row r="48" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6"/>
       <c r="B48" s="8" t="s">
         <v>83</v>
@@ -4711,7 +3749,7 @@
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
     </row>
-    <row r="49" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6"/>
       <c r="B49" s="8" t="s">
         <v>84</v>
@@ -4719,13 +3757,13 @@
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
     </row>
-    <row r="50" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -4733,7 +3771,7 @@
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6"/>
       <c r="B52" s="8" t="s">
         <v>86</v>
@@ -4741,7 +3779,7 @@
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6"/>
       <c r="B53" s="8" t="s">
         <v>87</v>
@@ -4749,7 +3787,7 @@
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
     </row>
-    <row r="54" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -4757,7 +3795,7 @@
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
     </row>
-    <row r="55" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6"/>
       <c r="B55" s="8" t="s">
         <v>89</v>
@@ -4765,7 +3803,7 @@
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
     </row>
-    <row r="56" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="8" t="s">
         <v>90</v>
@@ -4773,7 +3811,7 @@
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
     </row>
-    <row r="57" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6"/>
       <c r="B57" s="8" t="s">
         <v>91</v>
@@ -4781,7 +3819,7 @@
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
     </row>
-    <row r="58" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
       <c r="B58" s="8" t="s">
         <v>92</v>
@@ -4789,13 +3827,13 @@
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
     </row>
-    <row r="59" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
         <v>3</v>
       </c>
@@ -4805,7 +3843,7 @@
       <c r="C60" s="11"/>
       <c r="D60" s="8"/>
     </row>
-    <row r="61" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
       <c r="B61" s="8" t="s">
         <v>94</v>
@@ -4813,7 +3851,7 @@
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
     </row>
-    <row r="62" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6"/>
       <c r="B62" s="8" t="s">
         <v>95</v>
@@ -4821,13 +3859,13 @@
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
     </row>
-    <row r="63" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6"/>
       <c r="B64" s="8" t="s">
         <v>96</v>
@@ -4835,7 +3873,7 @@
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6"/>
       <c r="B65" s="8" t="s">
         <v>97</v>
@@ -4843,13 +3881,13 @@
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
     </row>
-    <row r="66" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6"/>
       <c r="B67" s="8" t="s">
         <v>98</v>
@@ -4857,7 +3895,7 @@
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
     </row>
-    <row r="68" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6"/>
       <c r="B68" s="8" t="s">
         <v>99</v>
@@ -4865,7 +3903,7 @@
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
     </row>
-    <row r="69" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6"/>
       <c r="B69" s="8" t="s">
         <v>100</v>
@@ -4873,7 +3911,7 @@
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
     </row>
-    <row r="70" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6"/>
       <c r="B70" s="8" t="s">
         <v>101</v>
@@ -4881,7 +3919,7 @@
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
     </row>
-    <row r="71" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
@@ -4891,7 +3929,7 @@
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
     </row>
-    <row r="72" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="6"/>
       <c r="B72" s="8" t="s">
         <v>103</v>
@@ -4899,7 +3937,7 @@
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6"/>
       <c r="B73" s="8" t="s">
         <v>104</v>
@@ -4907,7 +3945,7 @@
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
     </row>
-    <row r="74" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6"/>
       <c r="B74" s="8" t="s">
         <v>105</v>
@@ -4915,7 +3953,7 @@
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
     </row>
-    <row r="75" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>43</v>
       </c>
@@ -4925,7 +3963,7 @@
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
     </row>
-    <row r="76" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
       <c r="B76" s="15" t="s">
         <v>107</v>
@@ -4933,7 +3971,7 @@
       <c r="C76" s="15"/>
       <c r="D76" s="8"/>
     </row>
-    <row r="77" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6"/>
       <c r="B77" s="15" t="s">
         <v>108</v>
@@ -4941,13 +3979,13 @@
       <c r="C77" s="15"/>
       <c r="D77" s="8"/>
     </row>
-    <row r="78" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="8"/>
     </row>
-    <row r="79" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10">
         <v>4</v>
       </c>
@@ -4957,7 +3995,7 @@
       <c r="C79" s="11"/>
       <c r="D79" s="8"/>
     </row>
-    <row r="80" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6"/>
       <c r="B80" s="8" t="s">
         <v>110</v>
@@ -4965,7 +4003,7 @@
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6"/>
       <c r="B81" s="8" t="s">
         <v>111</v>
@@ -4973,7 +4011,7 @@
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6"/>
       <c r="B82" s="8" t="s">
         <v>112</v>
@@ -4981,7 +4019,7 @@
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6"/>
       <c r="B83" s="8" t="s">
         <v>113</v>
@@ -4989,13 +4027,13 @@
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
     </row>
-    <row r="84" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6"/>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
       <c r="D84" s="8"/>
     </row>
-    <row r="85" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6"/>
       <c r="B85" s="15" t="s">
         <v>114</v>
@@ -5003,7 +4041,7 @@
       <c r="C85" s="15"/>
       <c r="D85" s="8"/>
     </row>
-    <row r="86" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6"/>
       <c r="B86" s="15" t="s">
         <v>115</v>
@@ -5011,13 +4049,13 @@
       <c r="C86" s="15"/>
       <c r="D86" s="8"/>
     </row>
-    <row r="87" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6"/>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
       <c r="D87" s="8"/>
     </row>
-    <row r="88" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6"/>
       <c r="B88" s="15" t="s">
         <v>116</v>
@@ -5025,7 +4063,7 @@
       <c r="C88" s="15"/>
       <c r="D88" s="8"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6"/>
       <c r="B89" s="15" t="s">
         <v>117</v>
@@ -5033,13 +4071,13 @@
       <c r="C89" s="15"/>
       <c r="D89" s="8"/>
     </row>
-    <row r="90" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6"/>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
       <c r="D90" s="8"/>
     </row>
-    <row r="91" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6"/>
       <c r="B91" s="15" t="s">
         <v>118</v>
@@ -5047,13 +4085,13 @@
       <c r="C91" s="15"/>
       <c r="D91" s="8"/>
     </row>
-    <row r="92" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
       <c r="D92" s="8"/>
     </row>
-    <row r="93" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6"/>
       <c r="B93" s="15" t="s">
         <v>119</v>
@@ -5061,13 +4099,13 @@
       <c r="C93" s="15"/>
       <c r="D93" s="8"/>
     </row>
-    <row r="94" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6"/>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
       <c r="D94" s="8"/>
     </row>
-    <row r="95" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6"/>
       <c r="B95" s="15" t="s">
         <v>120</v>
@@ -5075,7 +4113,7 @@
       <c r="C95" s="15"/>
       <c r="D95" s="8"/>
     </row>
-    <row r="96" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="6"/>
       <c r="B96" s="8" t="s">
         <v>121</v>
@@ -5083,7 +4121,7 @@
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
     </row>
-    <row r="97" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="6"/>
       <c r="B97" s="8" t="s">
         <v>122</v>
@@ -5091,7 +4129,7 @@
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
     </row>
-    <row r="98" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="6"/>
       <c r="B98" s="8" t="s">
         <v>123</v>
@@ -5099,13 +4137,13 @@
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
     </row>
-    <row r="99" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="6"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
       <c r="D99" s="8"/>
     </row>
-    <row r="100" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="6"/>
       <c r="B100" s="8" t="s">
         <v>124</v>
@@ -5113,7 +4151,7 @@
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
     </row>
-    <row r="101" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="6"/>
       <c r="B101" s="8" t="s">
         <v>125</v>
@@ -5121,7 +4159,7 @@
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
     </row>
-    <row r="102" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="6"/>
       <c r="B102" s="8" t="s">
         <v>126</v>
@@ -5129,7 +4167,7 @@
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
     </row>
-    <row r="103" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="6"/>
       <c r="B103" s="8" t="s">
         <v>127</v>
@@ -5137,13 +4175,13 @@
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
     </row>
-    <row r="104" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="6"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
     </row>
-    <row r="105" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="6"/>
       <c r="B105" s="8" t="s">
         <v>128</v>
@@ -5151,7 +4189,7 @@
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
     </row>
-    <row r="106" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="6"/>
       <c r="B106" s="8" t="s">
         <v>277</v>
@@ -5159,7 +4197,7 @@
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
     </row>
-    <row r="107" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="6"/>
       <c r="B107" s="8" t="s">
         <v>129</v>
@@ -5167,7 +4205,7 @@
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
     </row>
-    <row r="108" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="6"/>
       <c r="B108" s="8" t="s">
         <v>130</v>
@@ -5175,57 +4213,57 @@
       <c r="C108" s="16"/>
       <c r="D108" s="8"/>
     </row>
-    <row r="109" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6"/>
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
       <c r="D109" s="8"/>
     </row>
-    <row r="110" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="6"/>
-      <c r="B110" s="102" t="s">
+      <c r="B110" s="110" t="s">
         <v>131</v>
       </c>
-      <c r="C110" s="102"/>
+      <c r="C110" s="110"/>
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="6"/>
-      <c r="B111" s="102"/>
-      <c r="C111" s="102"/>
+      <c r="B111" s="110"/>
+      <c r="C111" s="110"/>
       <c r="D111" s="1"/>
     </row>
-    <row r="112" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="6"/>
-      <c r="B112" s="102"/>
-      <c r="C112" s="102"/>
+      <c r="B112" s="110"/>
+      <c r="C112" s="110"/>
       <c r="D112" s="1"/>
     </row>
-    <row r="113" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="6"/>
-      <c r="B113" s="102"/>
-      <c r="C113" s="102"/>
+      <c r="B113" s="110"/>
+      <c r="C113" s="110"/>
       <c r="D113" s="18"/>
     </row>
-    <row r="114" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="6"/>
-      <c r="B114" s="102"/>
-      <c r="C114" s="102"/>
+      <c r="B114" s="110"/>
+      <c r="C114" s="110"/>
       <c r="D114" s="18"/>
     </row>
-    <row r="115" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
       <c r="B115" s="69"/>
       <c r="C115" s="69"/>
       <c r="D115" s="69"/>
     </row>
-    <row r="116" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="70"/>
       <c r="C116" s="70"/>
       <c r="D116" s="70"/>
     </row>
-    <row r="117" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="6"/>
       <c r="B117" s="70" t="s">
         <v>273</v>
@@ -5235,7 +4273,7 @@
       </c>
       <c r="D117" s="18"/>
     </row>
-    <row r="118" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="6"/>
       <c r="B118" s="70" t="s">
         <v>132</v>
@@ -5245,7 +4283,7 @@
       </c>
       <c r="D118" s="18"/>
     </row>
-    <row r="119" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6"/>
       <c r="B119" s="70" t="s">
         <v>265</v>
@@ -5255,7 +4293,7 @@
       </c>
       <c r="D119" s="18"/>
     </row>
-    <row r="120" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="6"/>
       <c r="B120" s="70" t="s">
         <v>134</v>
@@ -5265,7 +4303,7 @@
       </c>
       <c r="D120" s="18"/>
     </row>
-    <row r="121" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="6"/>
       <c r="B121" s="70" t="s">
         <v>267</v>
@@ -5275,7 +4313,7 @@
       </c>
       <c r="D121" s="18"/>
     </row>
-    <row r="122" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="6"/>
       <c r="B122" s="70" t="s">
         <v>137</v>
@@ -5285,7 +4323,7 @@
       </c>
       <c r="D122" s="18"/>
     </row>
-    <row r="123" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="6"/>
       <c r="B123" s="74"/>
       <c r="C123" s="75" t="s">
@@ -5293,19 +4331,19 @@
       </c>
       <c r="D123" s="18"/>
     </row>
-    <row r="124" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="10"/>
       <c r="B124" s="69"/>
       <c r="C124" s="69"/>
       <c r="D124" s="69"/>
     </row>
-    <row r="125" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="70"/>
       <c r="C125" s="70"/>
       <c r="D125" s="70"/>
     </row>
-    <row r="126" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="6"/>
       <c r="B126" s="74"/>
       <c r="C126" s="76"/>
@@ -5326,14 +4364,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -5355,7 +4393,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -5377,7 +4415,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -5395,7 +4433,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -5439,7 +4477,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -5483,7 +4521,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>3</v>
       </c>
@@ -5527,7 +4565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -5568,7 +4606,7 @@
         <v>0.393559682086012</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -5609,7 +4647,7 @@
         <v>0.87434286395628302</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -5650,7 +4688,7 @@
         <v>2.9033677587684901</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -5691,7 +4729,7 @@
         <v>11.914284608157899</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -5732,7 +4770,7 @@
         <v>15.8088974855476</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -5773,7 +4811,7 @@
         <v>18.9581829575793</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -5814,7 +4852,7 @@
         <v>11.3706308063368</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -5855,7 +4893,7 @@
         <v>11.4265524943328</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -5896,7 +4934,7 @@
         <v>12.2069899229245</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -5937,7 +4975,7 @@
         <v>14.1431914203104</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -5988,14 +5026,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -6017,7 +5055,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -6039,7 +5077,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -6057,7 +5095,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -6101,7 +5139,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -6145,7 +5183,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>4</v>
       </c>
@@ -6189,7 +5227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -6230,7 +5268,7 @@
         <v>1.1110250504958801</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -6271,7 +5309,7 @@
         <v>2.62241021394364</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -6312,7 +5350,7 @@
         <v>7.4889023824685701</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -6353,7 +5391,7 @@
         <v>19.9824744243165</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -6394,7 +5432,7 @@
         <v>16.841533599291399</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -6435,7 +5473,7 @@
         <v>15.6318703779553</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -6476,7 +5514,7 @@
         <v>7.9855548939090397</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -6517,7 +5555,7 @@
         <v>9.0231559258367202</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -6558,7 +5596,7 @@
         <v>9.7459233952454198</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -6599,7 +5637,7 @@
         <v>9.5671497365374201</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -6650,14 +5688,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -6679,7 +5717,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -6701,7 +5739,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -6719,7 +5757,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -6763,7 +5801,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -6807,7 +5845,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>5</v>
       </c>
@@ -6851,7 +5889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -6892,7 +5930,7 @@
         <v>0.78632260173834201</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -6933,7 +5971,7 @@
         <v>1.8200492898293099</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -6974,7 +6012,7 @@
         <v>5.5849877877838701</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -7015,7 +6053,7 @@
         <v>16.711929979799802</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -7056,7 +6094,7 @@
         <v>16.426901540807101</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -7097,7 +6135,7 @@
         <v>17.127885651110201</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -7138,7 +6176,7 @@
         <v>10.3506002591855</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -7179,7 +6217,7 @@
         <v>9.12213010035072</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -7220,7 +6258,7 @@
         <v>9.1950203510748807</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -7261,7 +6299,7 @@
         <v>12.874172438320199</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -7312,14 +6350,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -7341,7 +6379,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -7363,7 +6401,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -7381,7 +6419,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -7425,7 +6463,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -7469,7 +6507,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>6</v>
       </c>
@@ -7513,7 +6551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -7554,7 +6592,7 @@
         <v>2.0772356547691402</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -7595,7 +6633,7 @@
         <v>3.9724214917068301</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -7636,7 +6674,7 @@
         <v>8.8112640326153002</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -7677,7 +6715,7 @@
         <v>22.8237670755077</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -7718,7 +6756,7 @@
         <v>20.473073839383201</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -7759,7 +6797,7 @@
         <v>20.450354751304101</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -7800,7 +6838,7 @@
         <v>7.0706956658266202</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -7841,7 +6879,7 @@
         <v>5.5200769884173599</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -7882,7 +6920,7 @@
         <v>5.50149747437613</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -7923,7 +6961,7 @@
         <v>3.2996130260935801</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -7974,14 +7012,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -8003,7 +7041,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -8025,7 +7063,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -8043,7 +7081,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -8087,7 +7125,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -8131,7 +7169,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>7</v>
       </c>
@@ -8175,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -8216,7 +7254,7 @@
         <v>0.754618494074349</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -8257,7 +7295,7 @@
         <v>1.7039532776897599</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -8298,7 +7336,7 @@
         <v>5.0147294236139199</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -8339,7 +7377,7 @@
         <v>13.814849641825401</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -8380,7 +7418,7 @@
         <v>12.8252804034869</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -8421,7 +7459,7 @@
         <v>13.0805863223964</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -8462,7 +7500,7 @@
         <v>6.7651566407571897</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -8503,7 +7541,7 @@
         <v>6.7440923234495704</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -8544,7 +7582,7 @@
         <v>5.8545391612183497</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -8585,7 +7623,7 @@
         <v>33.442194311488201</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -8636,14 +7674,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -8665,7 +7703,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -8687,7 +7725,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -8705,7 +7743,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -8749,7 +7787,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -8793,7 +7831,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>8</v>
       </c>
@@ -8837,7 +7875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -8878,7 +7916,7 @@
         <v>3.1818147368416301</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -8919,7 +7957,7 @@
         <v>7.7558821406404199</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -8960,7 +7998,7 @@
         <v>20.720511112969302</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -9001,7 +8039,7 @@
         <v>35.441212598313797</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -9042,7 +8080,7 @@
         <v>14.4015633422429</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -9083,7 +8121,7 @@
         <v>5.3509388387786601</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -9124,7 +8162,7 @@
         <v>1.79151839379987</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -9165,7 +8203,7 @@
         <v>2.4601554069028699</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -9206,7 +8244,7 @@
         <v>0.872207504719969</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -9247,7 +8285,7 @@
         <v>8.0241959247906394</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -9298,14 +8336,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -9327,7 +8365,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -9349,7 +8387,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -9367,7 +8405,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -9411,7 +8449,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -9455,7 +8493,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>9</v>
       </c>
@@ -9499,7 +8537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -9540,7 +8578,7 @@
         <v>1.2210512252368599</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -9581,7 +8619,7 @@
         <v>2.7296302239175101</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -9622,7 +8660,7 @@
         <v>7.7881920155455102</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -9663,7 +8701,7 @@
         <v>18.119518720728301</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -9704,7 +8742,7 @@
         <v>16.051899407654702</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -9745,7 +8783,7 @@
         <v>14.5675729372817</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -9786,7 +8824,7 @@
         <v>6.9313610529292502</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -9827,7 +8865,7 @@
         <v>4.6778008298838598</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -9868,7 +8906,7 @@
         <v>1.73602184364651</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -9909,7 +8947,7 @@
         <v>26.176951743175799</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -9960,14 +8998,14 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -9989,7 +9027,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -10011,7 +9049,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -10029,7 +9067,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -10073,7 +9111,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -10117,7 +9155,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
@@ -10161,7 +9199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -10202,7 +9240,7 @@
         <v>4.2365556100875503</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -10243,7 +9281,7 @@
         <v>9.5658429780625092</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -10284,7 +9322,7 @@
         <v>22.4604023031266</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -10325,7 +9363,7 @@
         <v>32.443069094754399</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -10366,7 +9404,7 @@
         <v>12.688130850499901</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -10407,7 +9445,7 @@
         <v>9.3359391304674997</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -10448,7 +9486,7 @@
         <v>4.9034525507031601</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -10489,7 +9527,7 @@
         <v>4.3666074822982797</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -10530,7 +9568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -10571,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -10622,14 +9660,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -10651,7 +9689,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -10673,7 +9711,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -10691,7 +9729,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -10735,7 +9773,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -10779,7 +9817,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>11</v>
       </c>
@@ -10823,7 +9861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -10864,7 +9902,7 @@
         <v>0.74779672986053303</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -10905,7 +9943,7 @@
         <v>1.53487759056679</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -10946,7 +9984,7 @@
         <v>4.7865424844559197</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -10987,7 +10025,7 @@
         <v>14.943332532108199</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -11028,7 +10066,7 @@
         <v>16.952513277436601</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -11069,7 +10107,7 @@
         <v>19.457315563785301</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -11110,7 +10148,7 @@
         <v>7.9902392338080404</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -11151,7 +10189,7 @@
         <v>11.1797123161714</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -11192,7 +10230,7 @@
         <v>13.644961184589301</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -11233,7 +10271,7 @@
         <v>8.7627090872178393</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -11284,14 +10322,14 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -11313,7 +10351,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -11335,7 +10373,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -11353,7 +10391,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -11397,7 +10435,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -11441,7 +10479,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>12</v>
       </c>
@@ -11485,7 +10523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -11526,7 +10564,7 @@
         <v>4.9383524866028701</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -11567,7 +10605,7 @@
         <v>7.4911948823105199</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -11608,7 +10646,7 @@
         <v>15.9456048818663</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -11649,7 +10687,7 @@
         <v>26.0538994725473</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -11690,7 +10728,7 @@
         <v>17.9017818057035</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -11731,7 +10769,7 @@
         <v>14.6380450809629</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -11772,7 +10810,7 @@
         <v>4.8856287756409396</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -11813,7 +10851,7 @@
         <v>3.5322744689263201</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -11854,7 +10892,7 @@
         <v>2.26337268033233</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -11895,7 +10933,7 @@
         <v>2.3498454651070402</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -11946,16 +10984,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB9BD1E-DABE-4AF9-9A10-C863B4371E27}">
   <dimension ref="A1:H126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="20" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="68.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="9"/>
+    <col min="1" max="1" width="4.81640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="68.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="11.453125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>279</v>
       </c>
@@ -11963,13 +11001,13 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -11979,7 +11017,7 @@
       <c r="C3" s="11"/>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="8" t="s">
         <v>139</v>
@@ -11987,7 +11025,7 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
     </row>
-    <row r="5" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="8" t="s">
         <v>280</v>
@@ -11995,7 +11033,7 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="8" t="s">
         <v>140</v>
@@ -12003,7 +11041,7 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
         <v>141</v>
@@ -12011,7 +11049,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="8" t="s">
         <v>142</v>
@@ -12019,7 +11057,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="8" t="s">
         <v>143</v>
@@ -12027,13 +11065,13 @@
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>2</v>
       </c>
@@ -12043,7 +11081,7 @@
       <c r="C11" s="11"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="8" t="s">
         <v>145</v>
@@ -12051,7 +11089,7 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="8" t="s">
         <v>281</v>
@@ -12059,7 +11097,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="8" t="s">
         <v>146</v>
@@ -12067,7 +11105,7 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
       <c r="B15" s="8" t="s">
         <v>147</v>
@@ -12075,7 +11113,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
       <c r="B16" s="8" t="s">
         <v>148</v>
@@ -12083,7 +11121,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
       <c r="B17" s="8" t="s">
         <v>149</v>
@@ -12091,7 +11129,7 @@
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
       <c r="B18" s="8" t="s">
         <v>150</v>
@@ -12099,7 +11137,7 @@
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
       <c r="B19" s="8" t="s">
         <v>151</v>
@@ -12110,7 +11148,7 @@
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
       <c r="B20" s="8" t="s">
         <v>152</v>
@@ -12121,7 +11159,7 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6"/>
       <c r="B21" s="8" t="s">
         <v>153</v>
@@ -12132,7 +11170,7 @@
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
     </row>
-    <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
       <c r="B22" s="8" t="s">
         <v>154</v>
@@ -12143,7 +11181,7 @@
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
     </row>
-    <row r="23" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="8" t="s">
         <v>155</v>
@@ -12154,7 +11192,7 @@
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
       <c r="B24" s="8" t="s">
         <v>156</v>
@@ -12165,7 +11203,7 @@
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6"/>
       <c r="B25" s="8" t="s">
         <v>157</v>
@@ -12176,13 +11214,13 @@
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>
       <c r="B27" s="13" t="s">
         <v>158</v>
@@ -12192,7 +11230,7 @@
       <c r="F27" s="21"/>
       <c r="H27" s="21"/>
     </row>
-    <row r="28" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6"/>
       <c r="B28" s="14" t="s">
         <v>159</v>
@@ -12200,7 +11238,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6"/>
       <c r="B29" s="8" t="s">
         <v>160</v>
@@ -12208,7 +11246,7 @@
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6"/>
       <c r="B30" s="8" t="s">
         <v>161</v>
@@ -12216,7 +11254,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
       <c r="B31" s="8" t="s">
         <v>162</v>
@@ -12224,7 +11262,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
       <c r="B32" s="8" t="s">
         <v>163</v>
@@ -12232,13 +11270,13 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6"/>
       <c r="B34" s="13" t="s">
         <v>164</v>
@@ -12246,7 +11284,7 @@
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
     </row>
-    <row r="35" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6"/>
       <c r="B35" s="14" t="s">
         <v>165</v>
@@ -12254,7 +11292,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6"/>
       <c r="B36" s="8" t="s">
         <v>166</v>
@@ -12262,7 +11300,7 @@
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6"/>
       <c r="B37" s="8" t="s">
         <v>167</v>
@@ -12270,13 +11308,13 @@
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6"/>
       <c r="B39" s="13" t="s">
         <v>168</v>
@@ -12284,7 +11322,7 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6"/>
       <c r="B40" s="14" t="s">
         <v>169</v>
@@ -12292,7 +11330,7 @@
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
     </row>
-    <row r="41" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6"/>
       <c r="B41" s="14" t="s">
         <v>170</v>
@@ -12300,7 +11338,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6"/>
       <c r="B42" s="8" t="s">
         <v>171</v>
@@ -12308,7 +11346,7 @@
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
     </row>
-    <row r="43" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6"/>
       <c r="B43" s="8" t="s">
         <v>172</v>
@@ -12316,7 +11354,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6"/>
       <c r="B44" s="8" t="s">
         <v>173</v>
@@ -12324,7 +11362,7 @@
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
     </row>
-    <row r="45" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6"/>
       <c r="B45" s="8" t="s">
         <v>174</v>
@@ -12332,7 +11370,7 @@
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6"/>
       <c r="B46" s="8" t="s">
         <v>175</v>
@@ -12340,7 +11378,7 @@
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
     </row>
-    <row r="47" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6"/>
       <c r="B47" s="8" t="s">
         <v>176</v>
@@ -12348,13 +11386,13 @@
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
     </row>
-    <row r="48" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
     </row>
-    <row r="49" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6"/>
       <c r="B49" s="8" t="s">
         <v>177</v>
@@ -12362,7 +11400,7 @@
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
     </row>
-    <row r="50" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6"/>
       <c r="B50" s="8" t="s">
         <v>178</v>
@@ -12370,7 +11408,7 @@
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6"/>
       <c r="B51" s="8" t="s">
         <v>179</v>
@@ -12378,7 +11416,7 @@
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6"/>
       <c r="B52" s="8" t="s">
         <v>180</v>
@@ -12386,7 +11424,7 @@
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6"/>
       <c r="B53" s="8" t="s">
         <v>181</v>
@@ -12394,7 +11432,7 @@
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
     </row>
-    <row r="54" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6"/>
       <c r="B54" s="8" t="s">
         <v>182</v>
@@ -12402,7 +11440,7 @@
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
     </row>
-    <row r="55" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6"/>
       <c r="B55" s="8" t="s">
         <v>183</v>
@@ -12410,7 +11448,7 @@
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
     </row>
-    <row r="56" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="8" t="s">
         <v>184</v>
@@ -12418,7 +11456,7 @@
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
     </row>
-    <row r="57" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6"/>
       <c r="B57" s="8" t="s">
         <v>185</v>
@@ -12426,7 +11464,7 @@
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
     </row>
-    <row r="58" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
       <c r="B58" s="8" t="s">
         <v>186</v>
@@ -12434,13 +11472,13 @@
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
     </row>
-    <row r="59" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
         <v>3</v>
       </c>
@@ -12450,7 +11488,7 @@
       <c r="C60" s="11"/>
       <c r="D60" s="8"/>
     </row>
-    <row r="61" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
       <c r="B61" s="8" t="s">
         <v>188</v>
@@ -12458,7 +11496,7 @@
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
     </row>
-    <row r="62" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6"/>
       <c r="B62" s="8" t="s">
         <v>189</v>
@@ -12466,13 +11504,13 @@
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
     </row>
-    <row r="63" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6"/>
       <c r="B64" s="8" t="s">
         <v>190</v>
@@ -12480,7 +11518,7 @@
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6"/>
       <c r="B65" s="8" t="s">
         <v>191</v>
@@ -12488,13 +11526,13 @@
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
     </row>
-    <row r="66" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
     </row>
-    <row r="67" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6"/>
       <c r="B67" s="8" t="s">
         <v>192</v>
@@ -12502,7 +11540,7 @@
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
     </row>
-    <row r="68" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6"/>
       <c r="B68" s="8" t="s">
         <v>193</v>
@@ -12510,7 +11548,7 @@
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
     </row>
-    <row r="69" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6"/>
       <c r="B69" s="8" t="s">
         <v>194</v>
@@ -12518,7 +11556,7 @@
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
     </row>
-    <row r="70" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6"/>
       <c r="B70" s="8" t="s">
         <v>195</v>
@@ -12526,7 +11564,7 @@
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
     </row>
-    <row r="71" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
@@ -12536,7 +11574,7 @@
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
     </row>
-    <row r="72" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="6"/>
       <c r="B72" s="8" t="s">
         <v>197</v>
@@ -12544,7 +11582,7 @@
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
     </row>
-    <row r="73" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6"/>
       <c r="B73" s="15" t="s">
         <v>198</v>
@@ -12552,7 +11590,7 @@
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
     </row>
-    <row r="74" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6"/>
       <c r="B74" s="15" t="s">
         <v>199</v>
@@ -12560,7 +11598,7 @@
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
     </row>
-    <row r="75" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>43</v>
       </c>
@@ -12570,7 +11608,7 @@
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
     </row>
-    <row r="76" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
       <c r="B76" s="8" t="s">
         <v>201</v>
@@ -12578,7 +11616,7 @@
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
     </row>
-    <row r="77" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6"/>
       <c r="B77" s="15" t="s">
         <v>202</v>
@@ -12586,7 +11624,7 @@
       <c r="C77" s="15"/>
       <c r="D77" s="8"/>
     </row>
-    <row r="78" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6"/>
       <c r="B78" s="15" t="s">
         <v>203</v>
@@ -12594,13 +11632,13 @@
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
     </row>
-    <row r="79" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="8"/>
     </row>
-    <row r="80" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10">
         <v>4</v>
       </c>
@@ -12610,7 +11648,7 @@
       <c r="C80" s="11"/>
       <c r="D80" s="8"/>
     </row>
-    <row r="81" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6"/>
       <c r="B81" s="8" t="s">
         <v>205</v>
@@ -12618,7 +11656,7 @@
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
     </row>
-    <row r="82" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6"/>
       <c r="B82" s="8" t="s">
         <v>206</v>
@@ -12626,7 +11664,7 @@
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
     </row>
-    <row r="83" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6"/>
       <c r="B83" s="8" t="s">
         <v>207</v>
@@ -12634,7 +11672,7 @@
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
     </row>
-    <row r="84" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6"/>
       <c r="B84" s="8" t="s">
         <v>208</v>
@@ -12642,7 +11680,7 @@
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
     </row>
-    <row r="85" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6"/>
       <c r="B85" s="8" t="s">
         <v>209</v>
@@ -12650,13 +11688,13 @@
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
     </row>
-    <row r="86" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6"/>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
       <c r="D86" s="8"/>
     </row>
-    <row r="87" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6"/>
       <c r="B87" s="15" t="s">
         <v>210</v>
@@ -12664,13 +11702,13 @@
       <c r="C87" s="15"/>
       <c r="D87" s="8"/>
     </row>
-    <row r="88" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6"/>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
       <c r="D88" s="8"/>
     </row>
-    <row r="89" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6"/>
       <c r="B89" s="15" t="s">
         <v>211</v>
@@ -12678,7 +11716,7 @@
       <c r="C89" s="15"/>
       <c r="D89" s="8"/>
     </row>
-    <row r="90" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6"/>
       <c r="B90" s="15" t="s">
         <v>212</v>
@@ -12686,13 +11724,13 @@
       <c r="C90" s="15"/>
       <c r="D90" s="8"/>
     </row>
-    <row r="91" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6"/>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
       <c r="D91" s="8"/>
     </row>
-    <row r="92" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6"/>
       <c r="B92" s="15" t="s">
         <v>213</v>
@@ -12700,13 +11738,13 @@
       <c r="C92" s="15"/>
       <c r="D92" s="8"/>
     </row>
-    <row r="93" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6"/>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
       <c r="D93" s="8"/>
     </row>
-    <row r="94" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6"/>
       <c r="B94" s="15" t="s">
         <v>214</v>
@@ -12714,13 +11752,13 @@
       <c r="C94" s="15"/>
       <c r="D94" s="8"/>
     </row>
-    <row r="95" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
       <c r="D95" s="8"/>
     </row>
-    <row r="96" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="6"/>
       <c r="B96" s="8" t="s">
         <v>215</v>
@@ -12728,7 +11766,7 @@
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
     </row>
-    <row r="97" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="6"/>
       <c r="B97" s="8" t="s">
         <v>216</v>
@@ -12736,7 +11774,7 @@
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
     </row>
-    <row r="98" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="6"/>
       <c r="B98" s="8" t="s">
         <v>217</v>
@@ -12744,19 +11782,19 @@
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
     </row>
-    <row r="99" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="6"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
     </row>
-    <row r="100" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="6"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
     </row>
-    <row r="101" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="6"/>
       <c r="B101" s="8" t="s">
         <v>218</v>
@@ -12764,7 +11802,7 @@
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
     </row>
-    <row r="102" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="6"/>
       <c r="B102" s="8" t="s">
         <v>219</v>
@@ -12772,7 +11810,7 @@
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
     </row>
-    <row r="103" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="6"/>
       <c r="B103" s="8" t="s">
         <v>220</v>
@@ -12780,7 +11818,7 @@
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
     </row>
-    <row r="104" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="6"/>
       <c r="B104" s="8" t="s">
         <v>221</v>
@@ -12788,13 +11826,13 @@
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
     </row>
-    <row r="105" spans="1:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="8.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="6"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
     </row>
-    <row r="106" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="6"/>
       <c r="B106" s="8" t="s">
         <v>222</v>
@@ -12802,7 +11840,7 @@
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
     </row>
-    <row r="107" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="6"/>
       <c r="B107" s="8" t="s">
         <v>223</v>
@@ -12810,7 +11848,7 @@
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
     </row>
-    <row r="108" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="6"/>
       <c r="B108" s="17" t="s">
         <v>282</v>
@@ -12818,57 +11856,57 @@
       <c r="C108" s="17"/>
       <c r="D108" s="8"/>
     </row>
-    <row r="109" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
     </row>
-    <row r="110" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="6"/>
-      <c r="B110" s="102" t="s">
+      <c r="B110" s="110" t="s">
         <v>224</v>
       </c>
-      <c r="C110" s="102"/>
-      <c r="D110" s="102"/>
-    </row>
-    <row r="111" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C110" s="110"/>
+      <c r="D110" s="110"/>
+    </row>
+    <row r="111" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="6"/>
-      <c r="B111" s="102"/>
-      <c r="C111" s="102"/>
-      <c r="D111" s="102"/>
-    </row>
-    <row r="112" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="110"/>
+      <c r="C111" s="110"/>
+      <c r="D111" s="110"/>
+    </row>
+    <row r="112" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="6"/>
-      <c r="B112" s="102"/>
-      <c r="C112" s="102"/>
-      <c r="D112" s="102"/>
-    </row>
-    <row r="113" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="110"/>
+      <c r="C112" s="110"/>
+      <c r="D112" s="110"/>
+    </row>
+    <row r="113" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="6"/>
-      <c r="B113" s="102"/>
-      <c r="C113" s="102"/>
-      <c r="D113" s="102"/>
-    </row>
-    <row r="114" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="110"/>
+      <c r="C113" s="110"/>
+      <c r="D113" s="110"/>
+    </row>
+    <row r="114" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="6"/>
-      <c r="B114" s="102"/>
-      <c r="C114" s="102"/>
-      <c r="D114" s="102"/>
-    </row>
-    <row r="115" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="110"/>
+      <c r="C114" s="110"/>
+      <c r="D114" s="110"/>
+    </row>
+    <row r="115" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
       <c r="B115" s="19"/>
       <c r="C115" s="19"/>
       <c r="D115" s="19"/>
     </row>
-    <row r="116" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="22"/>
       <c r="C116" s="22"/>
       <c r="D116" s="22"/>
     </row>
-    <row r="117" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="6"/>
       <c r="B117" s="70" t="s">
         <v>225</v>
@@ -12878,7 +11916,7 @@
       </c>
       <c r="D117" s="8"/>
     </row>
-    <row r="118" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="6"/>
       <c r="B118" s="70" t="s">
         <v>226</v>
@@ -12888,7 +11926,7 @@
       </c>
       <c r="D118" s="8"/>
     </row>
-    <row r="119" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6"/>
       <c r="B119" s="70" t="s">
         <v>227</v>
@@ -12898,7 +11936,7 @@
       </c>
       <c r="D119" s="8"/>
     </row>
-    <row r="120" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="6"/>
       <c r="B120" s="70" t="s">
         <v>228</v>
@@ -12908,7 +11946,7 @@
       </c>
       <c r="D120" s="8"/>
     </row>
-    <row r="121" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="6"/>
       <c r="B121" s="70" t="s">
         <v>230</v>
@@ -12918,7 +11956,7 @@
       </c>
       <c r="D121" s="8"/>
     </row>
-    <row r="122" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="6"/>
       <c r="B122" s="70" t="s">
         <v>137</v>
@@ -12928,7 +11966,7 @@
       </c>
       <c r="D122" s="8"/>
     </row>
-    <row r="123" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="6"/>
       <c r="B123" s="74"/>
       <c r="C123" s="74" t="s">
@@ -12936,19 +11974,19 @@
       </c>
       <c r="D123" s="8"/>
     </row>
-    <row r="124" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="10"/>
       <c r="B124" s="69"/>
       <c r="C124" s="69"/>
       <c r="D124" s="69"/>
     </row>
-    <row r="125" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="70"/>
       <c r="C125" s="70"/>
       <c r="D125" s="70"/>
     </row>
-    <row r="126" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="6"/>
       <c r="B126" s="74"/>
       <c r="C126" s="76"/>
@@ -12969,14 +12007,14 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -12998,7 +12036,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -13020,7 +12058,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -13038,7 +12076,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -13082,7 +12120,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -13126,7 +12164,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>13</v>
       </c>
@@ -13170,7 +12208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -13211,7 +12249,7 @@
         <v>8.1824845514606501</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -13252,7 +12290,7 @@
         <v>11.782393598153901</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -13293,7 +12331,7 @@
         <v>18.067805832575701</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -13334,7 +12372,7 @@
         <v>21.2095307778959</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -13375,7 +12413,7 @@
         <v>13.2974120631934</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -13416,7 +12454,7 @@
         <v>6.3229835146588496</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -13457,7 +12495,7 @@
         <v>5.0991956936957097</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -13498,7 +12536,7 @@
         <v>2.5270578061945099</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -13539,7 +12577,7 @@
         <v>7.4527707238196799</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -13580,7 +12618,7 @@
         <v>6.0583654383517</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -13631,14 +12669,14 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -13660,7 +12698,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -13682,7 +12720,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -13700,7 +12738,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -13744,7 +12782,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -13788,7 +12826,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>14</v>
       </c>
@@ -13832,7 +12870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -13873,7 +12911,7 @@
         <v>0.82642828822649195</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -13914,7 +12952,7 @@
         <v>1.2302133993986599</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -13955,7 +12993,7 @@
         <v>3.47494288805269</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -13996,7 +13034,7 @@
         <v>12.302442616974</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -14037,7 +13075,7 @@
         <v>17.6603805723487</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -14078,7 +13116,7 @@
         <v>21.997079704623602</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -14119,7 +13157,7 @@
         <v>11.672087801358099</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -14160,7 +13198,7 @@
         <v>11.0920287009425</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -14201,7 +13239,7 @@
         <v>10.298442372574399</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -14242,7 +13280,7 @@
         <v>9.4459536555008103</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -14293,14 +13331,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -14322,7 +13360,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -14344,7 +13382,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -14362,7 +13400,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -14406,7 +13444,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -14450,7 +13488,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>15</v>
       </c>
@@ -14494,7 +13532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -14535,7 +13573,7 @@
         <v>5.1545605486368302</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -14576,7 +13614,7 @@
         <v>6.3413716680869898</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -14617,7 +13655,7 @@
         <v>12.0088299548593</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -14658,7 +13696,7 @@
         <v>15.889436631896199</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -14699,7 +13737,7 @@
         <v>11.298118408907699</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -14740,7 +13778,7 @@
         <v>11.540958199899199</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -14781,7 +13819,7 @@
         <v>3.6095967110567302</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -14822,7 +13860,7 @@
         <v>3.9422060947358499</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -14863,7 +13901,7 @@
         <v>1.96700331348341</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -14904,7 +13942,7 @@
         <v>28.247918468437799</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -14955,14 +13993,14 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -14984,7 +14022,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -15006,7 +14044,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -15024,7 +14062,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -15068,7 +14106,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -15112,7 +14150,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>16</v>
       </c>
@@ -15156,7 +14194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -15197,7 +14235,7 @@
         <v>2.1070749946420602</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -15238,7 +14276,7 @@
         <v>4.0274945970772897</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -15279,7 +14317,7 @@
         <v>10.069377512468201</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -15320,7 +14358,7 @@
         <v>25.195169125033001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -15361,7 +14399,7 @@
         <v>21.794867972572298</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -15402,7 +14440,7 @@
         <v>17.834523119196401</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -15443,7 +14481,7 @@
         <v>8.3487318370973398</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -15484,7 +14522,7 @@
         <v>4.8203965575660703</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -15525,7 +14563,7 @@
         <v>2.3383584496082102</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -15566,7 +14604,7 @@
         <v>3.4640058347390701</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -15617,14 +14655,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -15646,7 +14684,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -15668,7 +14706,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -15686,7 +14724,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -15730,7 +14768,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -15774,7 +14812,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>17</v>
       </c>
@@ -15818,7 +14856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -15859,7 +14897,7 @@
         <v>2.0933675185158598</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -15900,7 +14938,7 @@
         <v>4.7640198246561001</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -15941,7 +14979,7 @@
         <v>13.3206258512124</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -15982,7 +15020,7 @@
         <v>30.143423127408099</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -16023,7 +15061,7 @@
         <v>21.8823021594363</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -16064,7 +15102,7 @@
         <v>12.1792204404763</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -16105,7 +15143,7 @@
         <v>7.3928245273554403</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -16146,7 +15184,7 @@
         <v>3.6920909628116698</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -16187,7 +15225,7 @@
         <v>4.5321255881277303</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -16228,7 +15266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -16279,14 +15317,14 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -16308,7 +15346,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -16330,7 +15368,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -16348,7 +15386,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -16392,7 +15430,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -16436,7 +15474,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>18</v>
       </c>
@@ -16480,7 +15518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -16521,7 +15559,7 @@
         <v>2.0955244554447301</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -16562,7 +15600,7 @@
         <v>4.7038329259047504</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -16603,7 +15641,7 @@
         <v>12.8717114354417</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -16644,7 +15682,7 @@
         <v>35.106462938331198</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -16685,7 +15723,7 @@
         <v>25.332293998693</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -16726,7 +15764,7 @@
         <v>13.9314396558221</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -16767,7 +15805,7 @@
         <v>4.5661640361850404</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -16808,7 +15846,7 @@
         <v>1.3925705541775499</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -16849,7 +15887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -16890,7 +15928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -16941,14 +15979,14 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -16970,7 +16008,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -16992,7 +16030,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -17010,7 +16048,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -17054,7 +16092,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -17098,7 +16136,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>19</v>
       </c>
@@ -17142,7 +16180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -17183,7 +16221,7 @@
         <v>1.17063575475602</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -17224,7 +16262,7 @@
         <v>2.6166824859637701</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -17265,7 +16303,7 @@
         <v>7.9472426665418903</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -17306,7 +16344,7 @@
         <v>23.493825796644401</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -17347,7 +16385,7 @@
         <v>18.9140905057894</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -17388,7 +16426,7 @@
         <v>15.816401606889199</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -17429,7 +16467,7 @@
         <v>7.0505274035171697</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -17470,7 +16508,7 @@
         <v>8.0203452940933708</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -17511,7 +16549,7 @@
         <v>6.2568475646639401</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -17552,7 +16590,7 @@
         <v>8.7134009211409005</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -17603,14 +16641,14 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -17632,7 +16670,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -17654,7 +16692,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -17672,7 +16710,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -17716,7 +16754,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -17760,7 +16798,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>20</v>
       </c>
@@ -17804,7 +16842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -17845,7 +16883,7 @@
         <v>1.1406046607882701</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -17886,7 +16924,7 @@
         <v>3.0566448531707602</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -17927,7 +16965,7 @@
         <v>9.1519277324215995</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -17968,7 +17006,7 @@
         <v>24.707834466246702</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -18009,7 +17047,7 @@
         <v>17.5354160757282</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -18050,7 +17088,7 @@
         <v>9.9728348699304998</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -18091,7 +17129,7 @@
         <v>3.3588416954106801</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -18132,7 +17170,7 @@
         <v>2.9233884095748701</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -18173,7 +17211,7 @@
         <v>2.03298579602296</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -18214,7 +17252,7 @@
         <v>26.119521440705501</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -18265,14 +17303,14 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -18294,7 +17332,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -18316,7 +17354,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -18334,7 +17372,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -18378,7 +17416,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -18422,7 +17460,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>21</v>
       </c>
@@ -18466,7 +17504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -18507,7 +17545,7 @@
         <v>2.2872193294879</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -18548,7 +17586,7 @@
         <v>4.3139768448756604</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -18589,7 +17627,7 @@
         <v>10.5396975662991</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -18630,7 +17668,7 @@
         <v>26.8399436170202</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -18671,7 +17709,7 @@
         <v>19.728610390215099</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -18712,7 +17750,7 @@
         <v>14.0377286721896</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -18753,7 +17791,7 @@
         <v>6.97462597540739</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -18794,7 +17832,7 @@
         <v>6.1802854461199104</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -18835,7 +17873,7 @@
         <v>6.5631419914285303</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -18876,7 +17914,7 @@
         <v>2.53477016695664</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -18927,14 +17965,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -18956,7 +17994,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -18978,7 +18016,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -18996,7 +18034,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -19040,7 +18078,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -19084,7 +18122,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>22</v>
       </c>
@@ -19128,7 +18166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -19169,7 +18207,7 @@
         <v>1.2810386156619999</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -19210,7 +18248,7 @@
         <v>3.21952514512666</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -19251,7 +18289,7 @@
         <v>8.3572357829197799</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -19292,7 +18330,7 @@
         <v>22.3666556633497</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -19333,7 +18371,7 @@
         <v>19.3468515201772</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -19374,7 +18412,7 @@
         <v>16.523043753385899</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -19415,7 +18453,7 @@
         <v>7.8251160373705204</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -19456,7 +18494,7 @@
         <v>7.6252986802498697</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -19497,7 +18535,7 @@
         <v>5.5504263965310798</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -19538,7 +18576,7 @@
         <v>7.9048084052272998</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -19589,26 +18627,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="28" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" style="28" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="28" customWidth="1"/>
+    <col min="4" max="4" width="26.81640625" style="28" customWidth="1"/>
     <col min="5" max="5" width="27" style="28" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="25.26953125" style="28" customWidth="1"/>
     <col min="7" max="7" width="25" style="28" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="28" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" style="28" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" style="28" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" style="28" customWidth="1"/>
-    <col min="12" max="12" width="22.42578125" style="28" customWidth="1"/>
-    <col min="13" max="13" width="22.85546875" style="28" customWidth="1"/>
-    <col min="14" max="14" width="30.5703125" style="28" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="28"/>
+    <col min="8" max="8" width="19.1796875" style="28" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" style="28" customWidth="1"/>
+    <col min="10" max="10" width="20.54296875" style="28" customWidth="1"/>
+    <col min="11" max="11" width="25.54296875" style="28" customWidth="1"/>
+    <col min="12" max="12" width="22.453125" style="28" customWidth="1"/>
+    <col min="13" max="13" width="22.81640625" style="28" customWidth="1"/>
+    <col min="14" max="14" width="30.54296875" style="28" customWidth="1"/>
+    <col min="15" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -19629,7 +18667,7 @@
       <c r="L1" s="26"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -19650,7 +18688,7 @@
       <c r="L2" s="29"/>
       <c r="M2" s="30"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="25">
         <v>2022</v>
       </c>
@@ -19667,7 +18705,7 @@
       <c r="L3" s="29"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="42"/>
       <c r="B4" s="52"/>
       <c r="C4" s="53"/>
@@ -19682,7 +18720,7 @@
       <c r="L4" s="53"/>
       <c r="M4" s="54"/>
     </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
         <v>232</v>
       </c>
@@ -19723,7 +18761,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -19738,7 +18776,7 @@
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>231</v>
       </c>
@@ -19779,7 +18817,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
         <v>3</v>
       </c>
@@ -19820,7 +18858,7 @@
         <v>12.346063221909301</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="38" t="s">
         <v>4</v>
       </c>
@@ -19861,7 +18899,7 @@
         <v>9.6301281110013495</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
         <v>5</v>
       </c>
@@ -19902,7 +18940,7 @@
         <v>3.7046124380448502</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="38" t="s">
         <v>6</v>
       </c>
@@ -19943,7 +18981,7 @@
         <v>0.65458180157743295</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35" t="s">
         <v>7</v>
       </c>
@@ -19984,7 +19022,7 @@
         <v>3.0920191779780901</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="s">
         <v>8</v>
       </c>
@@ -20025,7 +19063,7 @@
         <v>0.55213923848922097</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>9</v>
       </c>
@@ -20066,7 +19104,7 @@
         <v>0.69021642708102504</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
         <v>10</v>
       </c>
@@ -20107,7 +19145,7 @@
         <v>0.46486334990299399</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
         <v>11</v>
       </c>
@@ -20148,7 +19186,7 @@
         <v>1.4901856168640899</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="38" t="s">
         <v>12</v>
       </c>
@@ -20189,7 +19227,7 @@
         <v>1.33704563316556</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
         <v>13</v>
       </c>
@@ -20230,7 +19268,7 @@
         <v>0.35938977445609899</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="38" t="s">
         <v>14</v>
       </c>
@@ -20271,7 +19309,7 @@
         <v>3.1410114891562899</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="35" t="s">
         <v>15</v>
       </c>
@@ -20312,7 +19350,7 @@
         <v>0.61194925483249796</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>16</v>
       </c>
@@ -20353,7 +19391,7 @@
         <v>0.64563676559653105</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35" t="s">
         <v>17</v>
       </c>
@@ -20394,7 +19432,7 @@
         <v>0.69890938132041902</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="38" t="s">
         <v>18</v>
       </c>
@@ -20435,7 +19473,7 @@
         <v>0.20755731737739899</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="35" t="s">
         <v>19</v>
       </c>
@@ -20476,7 +19514,7 @@
         <v>6.5428402499442004</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="38" t="s">
         <v>20</v>
       </c>
@@ -20517,7 +19555,7 @@
         <v>18.576145910110299</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="35" t="s">
         <v>21</v>
       </c>
@@ -20558,7 +19596,7 @@
         <v>2.8574281499247398</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="38" t="s">
         <v>22</v>
       </c>
@@ -20599,7 +19637,7 @@
         <v>2.6107979067122802</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="35" t="s">
         <v>23</v>
       </c>
@@ -20640,7 +19678,7 @@
         <v>4.7953043591449402</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="38" t="s">
         <v>24</v>
       </c>
@@ -20681,7 +19719,7 @@
         <v>11.175520483705601</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35" t="s">
         <v>25</v>
       </c>
@@ -20722,7 +19760,7 @@
         <v>5.8273469041146004</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
         <v>26</v>
       </c>
@@ -20763,7 +19801,7 @@
         <v>0.67460057054779199</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35" t="s">
         <v>27</v>
       </c>
@@ -20804,7 +19842,7 @@
         <v>7.1185675080049799</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="38" t="s">
         <v>28</v>
       </c>
@@ -20845,7 +19883,7 @@
         <v>0.19513895903744299</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="35" t="s">
         <v>29</v>
       </c>
@@ -20896,14 +19934,14 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -20925,7 +19963,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -20947,7 +19985,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -20965,7 +20003,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -21009,7 +20047,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -21053,7 +20091,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>23</v>
       </c>
@@ -21097,7 +20135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -21138,7 +20176,7 @@
         <v>4.4792186937237197</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -21179,7 +20217,7 @@
         <v>9.3736347843956604</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -21220,7 +20258,7 @@
         <v>19.0744962032195</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -21261,7 +20299,7 @@
         <v>29.593161905819699</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -21302,7 +20340,7 @@
         <v>15.559120856777</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -21343,7 +20381,7 @@
         <v>10.2616456339421</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -21384,7 +20422,7 @@
         <v>3.2861412311529001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -21425,7 +20463,7 @@
         <v>3.3677624691727002</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -21466,7 +20504,7 @@
         <v>3.5272060844001998</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -21507,7 +20545,7 @@
         <v>1.4776121373964699</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -21558,14 +20596,14 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -21587,7 +20625,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -21609,7 +20647,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -21627,7 +20665,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -21671,7 +20709,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -21715,7 +20753,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>24</v>
       </c>
@@ -21759,7 +20797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -21800,7 +20838,7 @@
         <v>1.0979299931672499</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -21841,7 +20879,7 @@
         <v>2.1777899918963701</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -21882,7 +20920,7 @@
         <v>5.8761557799630797</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -21923,7 +20961,7 @@
         <v>15.568623345985699</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -21964,7 +21002,7 @@
         <v>14.233314748242099</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -22005,7 +21043,7 @@
         <v>13.632678925623599</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -22046,7 +21084,7 @@
         <v>6.9686951093141998</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -22087,7 +21125,7 @@
         <v>6.7482730951645999</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -22128,7 +21166,7 @@
         <v>6.17687732351287</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -22169,7 +21207,7 @@
         <v>27.519661687130199</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -22220,14 +21258,14 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -22249,7 +21287,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -22271,7 +21309,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -22289,7 +21327,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -22333,7 +21371,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -22377,7 +21415,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>25</v>
       </c>
@@ -22421,7 +21459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -22462,7 +21500,7 @@
         <v>8.2204440752514198</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -22503,7 +21541,7 @@
         <v>14.632864123800999</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -22544,7 +21582,7 @@
         <v>22.404442876663801</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -22585,7 +21623,7 @@
         <v>27.404273419112702</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -22626,7 +21664,7 @@
         <v>14.7244700149758</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -22667,7 +21705,7 @@
         <v>7.6860323462852298</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -22708,7 +21746,7 @@
         <v>2.0641214538609298</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -22749,7 +21787,7 @@
         <v>1.7495210871690301</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -22790,7 +21828,7 @@
         <v>0.90555278622232305</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -22831,7 +21869,7 @@
         <v>0.208277816657677</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -22882,14 +21920,14 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -22911,7 +21949,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -22933,7 +21971,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -22951,7 +21989,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -22995,7 +22033,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -23039,7 +22077,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>26</v>
       </c>
@@ -23083,7 +22121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -23124,7 +22162,7 @@
         <v>3.4702945956801599</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -23165,7 +22203,7 @@
         <v>5.9391243834997001</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -23206,7 +22244,7 @@
         <v>13.1376859723732</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -23247,7 +22285,7 @@
         <v>25.5139001025574</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -23288,7 +22326,7 @@
         <v>21.0578506649513</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -23329,7 +22367,7 @@
         <v>15.4410864961622</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -23370,7 +22408,7 @@
         <v>6.0048455392425399</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -23411,7 +22449,7 @@
         <v>5.5334385465048799</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -23452,7 +22490,7 @@
         <v>3.9017736990285701</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -23493,7 +22531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -23544,14 +22582,14 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -23573,7 +22611,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -23595,7 +22633,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -23613,7 +22651,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -23657,7 +22695,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -23701,7 +22739,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>27</v>
       </c>
@@ -23745,7 +22783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -23786,7 +22824,7 @@
         <v>0.58075790171911701</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -23827,7 +22865,7 @@
         <v>0.721987562430354</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -23868,7 +22906,7 @@
         <v>1.6646701690151799</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -23909,7 +22947,7 @@
         <v>6.8974973252863601</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -23950,7 +22988,7 @@
         <v>9.9508754988873402</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -23991,7 +23029,7 @@
         <v>11.1239592809371</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -24032,7 +23070,7 @@
         <v>7.41466520926196</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -24073,7 +23111,7 @@
         <v>9.9052476580683706</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -24114,7 +23152,7 @@
         <v>14.0290999135246</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -24155,7 +23193,7 @@
         <v>37.7112394808697</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -24206,14 +23244,14 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -24235,7 +23273,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -24257,7 +23295,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -24275,7 +23313,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -24319,7 +23357,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -24363,7 +23401,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>28</v>
       </c>
@@ -24407,7 +23445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -24448,7 +23486,7 @@
         <v>8.0540910586164305</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -24489,7 +23527,7 @@
         <v>15.809454377339399</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -24530,7 +23568,7 @@
         <v>25.2518292628715</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -24571,7 +23609,7 @@
         <v>29.185522373463002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -24612,7 +23650,7 @@
         <v>12.416760759977601</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -24653,7 +23691,7 @@
         <v>6.0359006730264904</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -24694,7 +23732,7 @@
         <v>1.8257065889026201</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -24735,7 +23773,7 @@
         <v>1.4207349058029599</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -24776,7 +23814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -24817,7 +23855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -24868,14 +23906,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="37" width="16.7109375" style="28" customWidth="1"/>
-    <col min="38" max="16384" width="11.42578125" style="28"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="37" width="16.7265625" style="28" customWidth="1"/>
+    <col min="38" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -24940,7 +23978,7 @@
       <c r="AJ1" s="26"/>
       <c r="AK1" s="27"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -25005,7 +24043,7 @@
       <c r="AJ2" s="29"/>
       <c r="AK2" s="30"/>
     </row>
-    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -25070,7 +24108,7 @@
       <c r="AJ3" s="44"/>
       <c r="AK3" s="45"/>
     </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="47"/>
       <c r="B4" s="48" t="s">
         <v>240</v>
@@ -25133,7 +24171,7 @@
       <c r="AJ4" s="49"/>
       <c r="AK4" s="50"/>
     </row>
-    <row r="5" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
         <v>232</v>
       </c>
@@ -25246,7 +24284,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="51"/>
       <c r="B6" s="33" t="s">
         <v>241</v>
@@ -25309,7 +24347,7 @@
       <c r="AJ6" s="29"/>
       <c r="AK6" s="30"/>
     </row>
-    <row r="7" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>231</v>
       </c>
@@ -25422,7 +24460,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
         <v>3</v>
       </c>
@@ -25535,7 +24573,7 @@
         <v>25121</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="38" t="s">
         <v>4</v>
       </c>
@@ -25648,7 +24686,7 @@
         <v>36027</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
         <v>5</v>
       </c>
@@ -25761,7 +24799,7 @@
         <v>9654</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="38" t="s">
         <v>6</v>
       </c>
@@ -25874,7 +24912,7 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35" t="s">
         <v>7</v>
       </c>
@@ -25987,7 +25025,7 @@
         <v>7399</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="s">
         <v>8</v>
       </c>
@@ -26100,7 +25138,7 @@
         <v>4266</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>9</v>
       </c>
@@ -26213,7 +25251,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
         <v>10</v>
       </c>
@@ -26326,7 +25364,7 @@
         <v>3593</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
         <v>11</v>
       </c>
@@ -26439,7 +25477,7 @@
         <v>4189</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="38" t="s">
         <v>12</v>
       </c>
@@ -26552,7 +25590,7 @@
         <v>12700</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
         <v>13</v>
       </c>
@@ -26665,7 +25703,7 @@
         <v>7883</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="38" t="s">
         <v>14</v>
       </c>
@@ -26778,7 +25816,7 @@
         <v>8515</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="35" t="s">
         <v>15</v>
       </c>
@@ -26891,7 +25929,7 @@
         <v>8581</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>16</v>
       </c>
@@ -27004,7 +26042,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35" t="s">
         <v>17</v>
       </c>
@@ -27117,7 +26155,7 @@
         <v>3736</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="38" t="s">
         <v>18</v>
       </c>
@@ -27230,7 +26268,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="35" t="s">
         <v>19</v>
       </c>
@@ -27343,7 +26381,7 @@
         <v>21252</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="38" t="s">
         <v>20</v>
       </c>
@@ -27456,7 +26494,7 @@
         <v>63880</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="35" t="s">
         <v>21</v>
       </c>
@@ -27569,7 +26607,7 @@
         <v>16076</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="38" t="s">
         <v>22</v>
       </c>
@@ -27682,7 +26720,7 @@
         <v>10222</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="35" t="s">
         <v>23</v>
       </c>
@@ -27795,7 +26833,7 @@
         <v>42674</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="38" t="s">
         <v>24</v>
       </c>
@@ -27908,7 +26946,7 @@
         <v>33437</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35" t="s">
         <v>25</v>
       </c>
@@ -28021,7 +27059,7 @@
         <v>82270</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
         <v>26</v>
       </c>
@@ -28134,7 +27172,7 @@
         <v>5281</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35" t="s">
         <v>27</v>
       </c>
@@ -28247,7 +27285,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="38" t="s">
         <v>28</v>
       </c>
@@ -28360,7 +27398,7 @@
         <v>3168</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="35" t="s">
         <v>29</v>
       </c>
@@ -28473,7 +27511,7 @@
         <v>449208</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.78740157480314998" footer="0.78740157480314998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -28484,14 +27522,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AK35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="37" width="16.7109375" style="28" customWidth="1"/>
-    <col min="38" max="16384" width="11.42578125" style="28"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="37" width="16.7265625" style="28" customWidth="1"/>
+    <col min="38" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -28556,7 +27594,7 @@
       <c r="AJ1" s="26"/>
       <c r="AK1" s="27"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -28621,7 +27659,7 @@
       <c r="AJ2" s="29"/>
       <c r="AK2" s="30"/>
     </row>
-    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -28686,7 +27724,7 @@
       <c r="AJ3" s="44"/>
       <c r="AK3" s="45"/>
     </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="47"/>
       <c r="B4" s="48" t="s">
         <v>237</v>
@@ -28749,7 +27787,7 @@
       <c r="AJ4" s="49"/>
       <c r="AK4" s="50"/>
     </row>
-    <row r="5" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
         <v>232</v>
       </c>
@@ -28862,7 +27900,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="51"/>
       <c r="B6" s="33" t="s">
         <v>236</v>
@@ -28925,7 +27963,7 @@
       <c r="AJ6" s="29"/>
       <c r="AK6" s="30"/>
     </row>
-    <row r="7" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>231</v>
       </c>
@@ -29038,7 +28076,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
         <v>3</v>
       </c>
@@ -29151,7 +28189,7 @@
         <v>14232403000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="38" t="s">
         <v>4</v>
       </c>
@@ -29264,7 +28302,7 @@
         <v>11101503512</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
         <v>5</v>
       </c>
@@ -29377,7 +28415,7 @@
         <v>4270635605</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="38" t="s">
         <v>6</v>
       </c>
@@ -29490,7 +28528,7 @@
         <v>754594548</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35" t="s">
         <v>7</v>
       </c>
@@ -29603,7 +28641,7 @@
         <v>3564444976</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="s">
         <v>8</v>
       </c>
@@ -29716,7 +28754,7 @@
         <v>636499912</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>9</v>
       </c>
@@ -29829,7 +28867,7 @@
         <v>795673744</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
         <v>10</v>
       </c>
@@ -29942,7 +28980,7 @@
         <v>535889248</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
         <v>11</v>
       </c>
@@ -30055,7 +29093,7 @@
         <v>1717869240</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="38" t="s">
         <v>12</v>
       </c>
@@ -30168,7 +29206,7 @@
         <v>1541331187</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
         <v>13</v>
       </c>
@@ -30281,7 +29319,7 @@
         <v>414300495</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="38" t="s">
         <v>14</v>
       </c>
@@ -30394,7 +29432,7 @@
         <v>3620922762</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="35" t="s">
         <v>15</v>
       </c>
@@ -30507,7 +29545,7 @@
         <v>705448227</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>16</v>
       </c>
@@ -30620,7 +29658,7 @@
         <v>744282811</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35" t="s">
         <v>17</v>
       </c>
@@ -30733,7 +29771,7 @@
         <v>805694884</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="38" t="s">
         <v>18</v>
       </c>
@@ -30846,7 +29884,7 @@
         <v>239269744</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="35" t="s">
         <v>19</v>
       </c>
@@ -30959,7 +29997,7 @@
         <v>7542512745</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="38" t="s">
         <v>20</v>
       </c>
@@ -31072,7 +30110,7 @@
         <v>21414372341</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="35" t="s">
         <v>21</v>
       </c>
@@ -31185,7 +30223,7 @@
         <v>3294011074</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="38" t="s">
         <v>22</v>
       </c>
@@ -31298,7 +30336,7 @@
         <v>3009698500</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="35" t="s">
         <v>23</v>
       </c>
@@ -31411,7 +30449,7 @@
         <v>5527973000</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="38" t="s">
         <v>24</v>
       </c>
@@ -31524,7 +30562,7 @@
         <v>12883014480</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35" t="s">
         <v>25</v>
       </c>
@@ -31637,7 +30675,7 @@
         <v>6717700053</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
         <v>26</v>
       </c>
@@ -31750,7 +30788,7 @@
         <v>777671960</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35" t="s">
         <v>27</v>
       </c>
@@ -31863,7 +30901,7 @@
         <v>8206204661</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="38" t="s">
         <v>28</v>
       </c>
@@ -31976,7 +31014,7 @@
         <v>224954000</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="35" t="s">
         <v>29</v>
       </c>
@@ -32089,7 +31127,7 @@
         <v>115278876709</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.78740157480314998" footer="0.78740157480314998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -32100,14 +31138,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AK35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="37" width="16.7109375" style="28" customWidth="1"/>
-    <col min="38" max="16384" width="11.42578125" style="28"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="37" width="16.7265625" style="28" customWidth="1"/>
+    <col min="38" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -32172,7 +31210,7 @@
       <c r="AJ1" s="26"/>
       <c r="AK1" s="27"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -32237,7 +31275,7 @@
       <c r="AJ2" s="29"/>
       <c r="AK2" s="30"/>
     </row>
-    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -32302,7 +31340,7 @@
       <c r="AJ3" s="44"/>
       <c r="AK3" s="45"/>
     </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="47"/>
       <c r="B4" s="48" t="s">
         <v>242</v>
@@ -32365,7 +31403,7 @@
       <c r="AJ4" s="49"/>
       <c r="AK4" s="50"/>
     </row>
-    <row r="5" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
         <v>232</v>
       </c>
@@ -32478,7 +31516,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="51"/>
       <c r="B6" s="33" t="s">
         <v>243</v>
@@ -32541,7 +31579,7 @@
       <c r="AJ6" s="29"/>
       <c r="AK6" s="30"/>
     </row>
-    <row r="7" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>231</v>
       </c>
@@ -32654,7 +31692,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
         <v>3</v>
       </c>
@@ -32767,7 +31805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="38" t="s">
         <v>4</v>
       </c>
@@ -32880,7 +31918,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
         <v>5</v>
       </c>
@@ -32993,7 +32031,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="38" t="s">
         <v>6</v>
       </c>
@@ -33106,7 +32144,7 @@
         <v>99.935379644588096</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35" t="s">
         <v>7</v>
       </c>
@@ -33219,7 +32257,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="s">
         <v>8</v>
       </c>
@@ -33332,7 +32370,7 @@
         <v>99.812821712681298</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>9</v>
       </c>
@@ -33445,7 +32483,7 @@
         <v>99.915540540540505</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
         <v>10</v>
       </c>
@@ -33558,7 +32596,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
         <v>11</v>
       </c>
@@ -33671,7 +32709,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="38" t="s">
         <v>12</v>
       </c>
@@ -33784,7 +32822,7 @@
         <v>99.976383531449301</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
         <v>13</v>
       </c>
@@ -33897,7 +32935,7 @@
         <v>99.949283631292005</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="38" t="s">
         <v>14</v>
       </c>
@@ -34010,7 +33048,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="35" t="s">
         <v>15</v>
       </c>
@@ -34123,7 +33161,7 @@
         <v>99.976698124199004</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>16</v>
       </c>
@@ -34236,7 +33274,7 @@
         <v>99.845583693638105</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35" t="s">
         <v>17</v>
       </c>
@@ -34349,7 +33387,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="38" t="s">
         <v>18</v>
       </c>
@@ -34462,7 +33500,7 @@
         <v>99.4041708043694</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="35" t="s">
         <v>19</v>
       </c>
@@ -34575,7 +33613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="38" t="s">
         <v>20</v>
       </c>
@@ -34688,7 +33726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="35" t="s">
         <v>21</v>
       </c>
@@ -34801,7 +33839,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="38" t="s">
         <v>22</v>
       </c>
@@ -34914,7 +33952,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="35" t="s">
         <v>23</v>
       </c>
@@ -35027,7 +34065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="38" t="s">
         <v>24</v>
       </c>
@@ -35140,7 +34178,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35" t="s">
         <v>25</v>
       </c>
@@ -35253,7 +34291,7 @@
         <v>99.998784504868098</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
         <v>26</v>
       </c>
@@ -35366,7 +34404,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35" t="s">
         <v>27</v>
       </c>
@@ -35479,7 +34517,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="38" t="s">
         <v>28</v>
       </c>
@@ -35592,7 +34630,7 @@
         <v>99.905392620624397</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="35" t="s">
         <v>29</v>
       </c>
@@ -35705,7 +34743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.78740157480314998" footer="0.78740157480314998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -35716,14 +34754,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AK35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="37" width="16.7109375" style="28" customWidth="1"/>
-    <col min="38" max="16384" width="11.42578125" style="28"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="37" width="16.7265625" style="28" customWidth="1"/>
+    <col min="38" max="16384" width="11.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -35788,7 +34826,7 @@
       <c r="AJ1" s="26"/>
       <c r="AK1" s="27"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -35853,7 +34891,7 @@
       <c r="AJ2" s="29"/>
       <c r="AK2" s="30"/>
     </row>
-    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -35918,7 +34956,7 @@
       <c r="AJ3" s="44"/>
       <c r="AK3" s="45"/>
     </row>
-    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="47"/>
       <c r="B4" s="48" t="s">
         <v>262</v>
@@ -35981,7 +35019,7 @@
       <c r="AJ4" s="49"/>
       <c r="AK4" s="50"/>
     </row>
-    <row r="5" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
         <v>232</v>
       </c>
@@ -36094,7 +35132,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="51"/>
       <c r="B6" s="33" t="s">
         <v>263</v>
@@ -36157,7 +35195,7 @@
       <c r="AJ6" s="29"/>
       <c r="AK6" s="30"/>
     </row>
-    <row r="7" spans="1:37" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="23" t="s">
         <v>231</v>
       </c>
@@ -36270,7 +35308,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
         <v>3</v>
       </c>
@@ -36383,7 +35421,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="38" t="s">
         <v>4</v>
       </c>
@@ -36496,7 +35534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="35" t="s">
         <v>5</v>
       </c>
@@ -36609,7 +35647,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="38" t="s">
         <v>6</v>
       </c>
@@ -36722,7 +35760,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="35" t="s">
         <v>7</v>
       </c>
@@ -36835,7 +35873,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="s">
         <v>8</v>
       </c>
@@ -36948,7 +35986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35" t="s">
         <v>9</v>
       </c>
@@ -37061,7 +36099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
         <v>10</v>
       </c>
@@ -37174,7 +36212,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="35" t="s">
         <v>11</v>
       </c>
@@ -37287,7 +36325,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="38" t="s">
         <v>12</v>
       </c>
@@ -37400,7 +36438,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="35" t="s">
         <v>13</v>
       </c>
@@ -37513,7 +36551,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="38" t="s">
         <v>14</v>
       </c>
@@ -37626,7 +36664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="35" t="s">
         <v>15</v>
       </c>
@@ -37739,7 +36777,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>16</v>
       </c>
@@ -37852,7 +36890,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35" t="s">
         <v>17</v>
       </c>
@@ -37965,7 +37003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="38" t="s">
         <v>18</v>
       </c>
@@ -38078,7 +37116,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="35" t="s">
         <v>19</v>
       </c>
@@ -38191,7 +37229,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="38" t="s">
         <v>20</v>
       </c>
@@ -38304,7 +37342,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="35" t="s">
         <v>21</v>
       </c>
@@ -38417,7 +37455,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="38" t="s">
         <v>22</v>
       </c>
@@ -38530,7 +37568,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="35" t="s">
         <v>23</v>
       </c>
@@ -38643,7 +37681,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="38" t="s">
         <v>24</v>
       </c>
@@ -38756,7 +37794,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="35" t="s">
         <v>25</v>
       </c>
@@ -38869,7 +37907,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
         <v>26</v>
       </c>
@@ -38982,7 +38020,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="35" t="s">
         <v>27</v>
       </c>
@@ -39095,7 +38133,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="38" t="s">
         <v>28</v>
       </c>
@@ -39208,7 +38246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="35" t="s">
         <v>29</v>
       </c>
@@ -39321,7 +38359,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:37" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.78740157480314998" footer="0.78740157480314998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -39332,14 +38370,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="37.54296875" customWidth="1"/>
+    <col min="3" max="14" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>254</v>
       </c>
@@ -39361,7 +38399,7 @@
       <c r="M1" s="65"/>
       <c r="N1" s="66"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>255</v>
       </c>
@@ -39383,7 +38421,7 @@
       <c r="M2" s="67"/>
       <c r="N2" s="68"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="34">
         <v>2022</v>
       </c>
@@ -39401,7 +38439,7 @@
       <c r="M3" s="64"/>
       <c r="N3" s="64"/>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="59" t="s">
         <v>232</v>
       </c>
@@ -39445,7 +38483,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="57" t="s">
         <v>231</v>
       </c>
@@ -39489,7 +38527,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
         <v>29</v>
       </c>
@@ -39533,7 +38571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="56" t="s">
         <v>32</v>
       </c>
@@ -39574,7 +38612,7 @@
         <v>1.74826555439767</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="55" t="s">
         <v>33</v>
       </c>
@@ -39615,7 +38653,7 @@
         <v>3.5388511950008499</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="56" t="s">
         <v>34</v>
       </c>
@@ -39656,7 +38694,7 @@
         <v>8.3615401808017999</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>35</v>
       </c>
@@ -39697,7 +38735,7 @@
         <v>19.593424031201199</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56" t="s">
         <v>36</v>
       </c>
@@ -39738,7 +38776,7 @@
         <v>16.105117400532901</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="55" t="s">
         <v>37</v>
       </c>
@@ -39779,7 +38817,7 @@
         <v>13.7826352663962</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56" t="s">
         <v>38</v>
       </c>
@@ -39820,7 +38858,7 @@
         <v>6.7161451794364604</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="55" t="s">
         <v>39</v>
       </c>
@@ -39861,7 +38899,7 @@
         <v>6.7899956032351803</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56" t="s">
         <v>40</v>
       </c>
@@ -39902,7 +38940,7 @@
         <v>6.7194419230450801</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="55" t="s">
         <v>41</v>
       </c>
@@ -39943,7 +38981,7 @@
         <v>16.644583665952698</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -39994,28 +39032,28 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832BAC04-CCF2-4AFA-9296-BDFFB87210B6}">
   <dimension ref="A3:O31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="101" t="s">
+    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E3" s="109" t="s">
         <v>290</v>
       </c>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-    </row>
-    <row r="4" spans="1:13" ht="195.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+    </row>
+    <row r="4" spans="1:13" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>293</v>
       </c>
@@ -40056,7 +39094,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B5" s="58"/>
       <c r="C5" s="57"/>
       <c r="D5" s="85"/>
@@ -40078,7 +39116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0</v>
       </c>
@@ -40127,7 +39165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0</v>
       </c>
@@ -40177,7 +39215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>50000</v>
       </c>
@@ -40227,7 +39265,7 @@
         <v>-5.2510330472700442E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>100000</v>
       </c>
@@ -40277,7 +39315,7 @@
         <v>-1.2612250857788691E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>200000</v>
       </c>
@@ -40327,7 +39365,7 @@
         <v>-2.8251450869219045E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>500000</v>
       </c>
@@ -40377,7 +39415,7 @@
         <v>-7.7143234813562972E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1000000</v>
       </c>
@@ -40427,7 +39465,7 @@
         <v>-0.14701752386296574</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2000000</v>
       </c>
@@ -40477,24 +39515,24 @@
         <v>-0.23505666173988304</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" s="100" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="100">
         <v>3000000</v>
       </c>
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="104">
+      <c r="C14" s="102">
         <v>46731</v>
       </c>
-      <c r="D14" s="105">
+      <c r="D14" s="103">
         <v>178069824212</v>
       </c>
-      <c r="E14" s="106">
+      <c r="E14" s="104">
         <f>SUM(C$6:C14)/C$17</f>
         <v>0.99101781590673144</v>
       </c>
-      <c r="F14" s="106">
+      <c r="F14" s="104">
         <f>SUM(D$6:D14)/D$17</f>
         <v>0.55885441479972398</v>
       </c>
@@ -40502,7 +39540,7 @@
         <f t="shared" si="0"/>
         <v>0.81818181818181834</v>
       </c>
-      <c r="H14" s="107">
+      <c r="H14" s="105">
         <f t="shared" si="1"/>
         <v>0.81818181818181834</v>
       </c>
@@ -40527,24 +39565,24 @@
         <v>-0.28802853614698237</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" s="100" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="100">
         <v>5000000</v>
       </c>
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="109">
+      <c r="C15" s="107">
         <v>29665</v>
       </c>
-      <c r="D15" s="110">
+      <c r="D15" s="108">
         <v>203853271799</v>
       </c>
-      <c r="E15" s="106">
+      <c r="E15" s="104">
         <f>SUM(C$6:C15)/C$17</f>
         <v>0.99627959495741891</v>
       </c>
-      <c r="F15" s="106">
+      <c r="F15" s="104">
         <f>SUM(D$6:D15)/D$17</f>
         <v>0.64362550427687171</v>
       </c>
@@ -40552,7 +39590,7 @@
         <f t="shared" si="0"/>
         <v>0.90909090909090928</v>
       </c>
-      <c r="H15" s="107">
+      <c r="H15" s="105">
         <f t="shared" si="1"/>
         <v>0.90909090909090928</v>
       </c>
@@ -40577,7 +39615,7 @@
         <v>-0.35541806265226172</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>10000000</v>
       </c>
@@ -40624,7 +39662,7 @@
         <v>-0.44809338421722278</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B17" s="56" t="s">
         <v>30</v>
       </c>
@@ -40636,7 +39674,7 @@
       </c>
       <c r="E17" s="82"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="H18" s="100" t="s">
         <v>296</v>
       </c>
@@ -40645,7 +39683,7 @@
         <v>7.0327641644357411E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="H19" s="100" t="s">
         <v>295</v>
       </c>
@@ -40654,12 +39692,12 @@
         <v>0.85934471671128521</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="K20" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>292</v>
       </c>
@@ -40686,17 +39724,13 @@
         <v>305</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22">
         <f>LOG(D7/C7)</f>
         <v>4.2296500017809704</v>
       </c>
-      <c r="B22">
-        <f t="shared" ref="B22:B31" si="4">LOG(1-E6)</f>
-        <v>-0.10972341132993091</v>
-      </c>
       <c r="C22" s="84">
-        <f t="shared" ref="C22:C31" si="5">1-F6</f>
+        <f>1-F6</f>
         <v>1</v>
       </c>
       <c r="J22">
@@ -40724,48 +39758,36 @@
         <v>19318548.937281165</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23">
-        <f t="shared" ref="A23:A31" si="6">LOG(D8/C8)</f>
+        <f t="shared" ref="A23:A31" si="4">LOG(D8/C8)</f>
         <v>4.861858331794771</v>
       </c>
-      <c r="B23">
+      <c r="C23" s="84">
+        <f t="shared" ref="C22:C31" si="5">1-F7</f>
+        <v>0.98798185141369232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24">
         <f t="shared" si="4"/>
-        <v>-0.32363099174799626</v>
-      </c>
-      <c r="C23" s="84">
-        <f t="shared" si="5"/>
-        <v>0.98798185141369232</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <f t="shared" si="6"/>
         <v>5.1603849216713229</v>
-      </c>
-      <c r="B24">
-        <f t="shared" si="4"/>
-        <v>-0.42331954997525389</v>
       </c>
       <c r="C24" s="84">
         <f t="shared" si="5"/>
         <v>0.97137685011997044</v>
       </c>
       <c r="K24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L24" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5.5116282861558688</v>
-      </c>
-      <c r="B25">
-        <f t="shared" si="4"/>
-        <v>-0.55909433751016524</v>
       </c>
       <c r="C25" s="84">
         <f t="shared" si="5"/>
@@ -40780,45 +39802,33 @@
         <v>44.8385459630626</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5.8471955122603507</v>
-      </c>
-      <c r="B26">
-        <f t="shared" si="4"/>
-        <v>-0.83867658047400384</v>
       </c>
       <c r="C26" s="84">
         <f t="shared" si="5"/>
         <v>0.83725310185019364</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>6.1390666564394154</v>
-      </c>
-      <c r="B27">
-        <f t="shared" si="4"/>
-        <v>-1.1578223544713195</v>
       </c>
       <c r="C27" s="84">
         <f t="shared" si="5"/>
         <v>0.71282426695472589</v>
       </c>
       <c r="K27" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>6.3846619265652382</v>
-      </c>
-      <c r="B28">
-        <f t="shared" si="4"/>
-        <v>-1.5371877741882169</v>
       </c>
       <c r="C28" s="84">
         <f t="shared" si="5"/>
@@ -40829,42 +39839,30 @@
         <v>0.44163938948988618</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>6.5809852553487378</v>
-      </c>
-      <c r="B29">
-        <f t="shared" si="4"/>
-        <v>-1.7626821149285412</v>
       </c>
       <c r="C29" s="84">
         <f t="shared" si="5"/>
         <v>0.51519479161350112</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>6.8370733334990481</v>
-      </c>
-      <c r="B30">
-        <f t="shared" si="4"/>
-        <v>-2.0466180481520193</v>
       </c>
       <c r="C30" s="84">
         <f t="shared" si="5"/>
         <v>0.44114558520027602</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>7.6112745677132834</v>
-      </c>
-      <c r="B31">
-        <f t="shared" si="4"/>
-        <v>-2.4294097756605848</v>
       </c>
       <c r="C31" s="84">
         <f t="shared" si="5"/>
